--- a/data/trans_bre/P1802_2016_2023-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1802_2016_2023-Clase-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 4,84</t>
+          <t>-6,61; 4,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 9,36</t>
+          <t>1,5; 10,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 36,49</t>
+          <t>-34,26; 32,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 62,79</t>
+          <t>7,93; 72,46</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 10,03</t>
+          <t>-0,58; 9,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 9,1</t>
+          <t>0,01; 9,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 100,56</t>
+          <t>-4,73; 97,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 68,37</t>
+          <t>-0,33; 71,8</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-25,17</t>
+          <t>6,27</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-53,95%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 16,44</t>
+          <t>1,2; 17,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-57,37; 7,55</t>
+          <t>0,18; 13,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 116,55</t>
+          <t>6,68; 127,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-78,05; 47,57</t>
+          <t>0,56; 100,28</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,83%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 7,79</t>
+          <t>0,45; 7,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 4,57</t>
+          <t>0,89; 7,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 55,35</t>
+          <t>2,69; 53,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,42; 26,8</t>
+          <t>4,77; 48,91</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,71</t>
+          <t>0,81; 8,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 4,97</t>
+          <t>0,1; 7,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 74,27</t>
+          <t>5,87; 76,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 36,32</t>
+          <t>0,3; 60,66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,31</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205,07%</t>
+          <t>220,85%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,77</t>
+          <t>5,22; 13,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 12,79</t>
+          <t>4,98; 13,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,6; 205,39</t>
+          <t>38,08; 186,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,26; 654,85</t>
+          <t>52,19; 644,23</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-4,72</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-21,42%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,41</t>
+          <t>2,83; 6,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,63; 2,29</t>
+          <t>2,1; 5,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,44; 47,4</t>
+          <t>18,24; 46,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-60,03; 14,31</t>
+          <t>12,96; 37,92</t>
         </is>
       </c>
     </row>
